--- a/MS_Excel_Practical_Exam_Medium_Level (1).xlsx
+++ b/MS_Excel_Practical_Exam_Medium_Level (1).xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASDC16\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ef5c52687c3375dc/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B823E637-21E8-48D0-9B57-E317CF9060F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{454F888D-A056-46CB-9A78-2579E7DC50F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8970C27E-E027-470E-A653-533A308E8C97}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="80">
   <si>
     <t>Total Questions: 30</t>
   </si>
@@ -287,6 +287,18 @@
   </si>
   <si>
     <t xml:space="preserve">                  FINALIST</t>
+  </si>
+  <si>
+    <t>NORTH</t>
+  </si>
+  <si>
+    <t>SOUTH</t>
+  </si>
+  <si>
+    <t>EAST</t>
+  </si>
+  <si>
+    <t>WEST</t>
   </si>
 </sst>
 </file>
@@ -1303,7 +1315,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38447B1B-1101-43C5-A550-371CDC84FF30}">
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.1796875" customWidth="1"/>
@@ -1630,7 +1642,10 @@
       <c r="I23" s="3">
         <v>0.18</v>
       </c>
-      <c r="J23" s="1"/>
+      <c r="J23" s="1">
+        <f>H23*I23</f>
+        <v>16200</v>
+      </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24">
@@ -1660,7 +1675,10 @@
       <c r="I24" s="3">
         <v>0.12</v>
       </c>
-      <c r="J24" s="1"/>
+      <c r="J24" s="1">
+        <f t="shared" ref="J24:J28" si="0">H24*I24</f>
+        <v>9000</v>
+      </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25">
@@ -1690,7 +1708,10 @@
       <c r="I25" s="3">
         <v>0.12</v>
       </c>
-      <c r="J25" s="1"/>
+      <c r="J25" s="1">
+        <f t="shared" si="0"/>
+        <v>6480</v>
+      </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26">
@@ -1720,7 +1741,10 @@
       <c r="I26" s="3">
         <v>0.18</v>
       </c>
-      <c r="J26" s="1"/>
+      <c r="J26" s="1">
+        <f t="shared" si="0"/>
+        <v>8100</v>
+      </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27">
@@ -1750,7 +1774,10 @@
       <c r="I27" s="3">
         <v>0.12</v>
       </c>
-      <c r="J27" s="1"/>
+      <c r="J27" s="1">
+        <f t="shared" si="0"/>
+        <v>7200</v>
+      </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28">
@@ -1780,7 +1807,10 @@
       <c r="I28" s="3">
         <v>0.18</v>
       </c>
-      <c r="J28" s="1"/>
+      <c r="J28" s="1">
+        <f t="shared" si="0"/>
+        <v>16200</v>
+      </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
@@ -1790,29 +1820,242 @@
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
     </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" t="s">
+        <v>7</v>
+      </c>
+      <c r="E33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" t="s">
+        <v>73</v>
+      </c>
+      <c r="G33" t="s">
+        <v>9</v>
+      </c>
+      <c r="H33" t="e" cm="1">
+        <f t="array" ref="H33:H39">E33:E39*F33:F39</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="I33" t="s">
+        <v>74</v>
+      </c>
+      <c r="J33" t="s">
+        <v>75</v>
+      </c>
+    </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="H34" s="1"/>
-      <c r="J34" s="1"/>
+      <c r="A34">
+        <v>301</v>
+      </c>
+      <c r="B34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34">
+        <v>2</v>
+      </c>
+      <c r="F34">
+        <v>45000</v>
+      </c>
+      <c r="G34" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" s="1">
+        <v>90000</v>
+      </c>
+      <c r="I34" s="3">
+        <v>0.18</v>
+      </c>
+      <c r="J34" s="1">
+        <f>H34*I34</f>
+        <v>16200</v>
+      </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="H35" s="1"/>
-      <c r="J35" s="1"/>
+      <c r="A35">
+        <v>302</v>
+      </c>
+      <c r="B35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35">
+        <v>5</v>
+      </c>
+      <c r="F35">
+        <v>15000</v>
+      </c>
+      <c r="G35" t="s">
+        <v>17</v>
+      </c>
+      <c r="H35" s="1">
+        <v>75000</v>
+      </c>
+      <c r="I35" s="3">
+        <v>0.12</v>
+      </c>
+      <c r="J35" s="1">
+        <f t="shared" ref="J35:J39" si="1">H35*I35</f>
+        <v>9000</v>
+      </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="H36" s="1"/>
-      <c r="J36" s="1"/>
+      <c r="A36">
+        <v>303</v>
+      </c>
+      <c r="B36" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36">
+        <v>3</v>
+      </c>
+      <c r="F36">
+        <v>18000</v>
+      </c>
+      <c r="G36" t="s">
+        <v>21</v>
+      </c>
+      <c r="H36" s="1">
+        <v>54000</v>
+      </c>
+      <c r="I36" s="3">
+        <v>0.12</v>
+      </c>
+      <c r="J36" s="1">
+        <f t="shared" si="1"/>
+        <v>6480</v>
+      </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="H37" s="1"/>
-      <c r="J37" s="1"/>
+      <c r="A37">
+        <v>304</v>
+      </c>
+      <c r="B37" t="s">
+        <v>22</v>
+      </c>
+      <c r="C37" t="s">
+        <v>23</v>
+      </c>
+      <c r="D37" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+      <c r="F37">
+        <v>45000</v>
+      </c>
+      <c r="G37" t="s">
+        <v>24</v>
+      </c>
+      <c r="H37" s="1">
+        <v>45000</v>
+      </c>
+      <c r="I37" s="3">
+        <v>0.18</v>
+      </c>
+      <c r="J37" s="1">
+        <f t="shared" si="1"/>
+        <v>8100</v>
+      </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="H38" s="1"/>
-      <c r="J38" s="1"/>
+      <c r="A38">
+        <v>305</v>
+      </c>
+      <c r="B38" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" t="s">
+        <v>16</v>
+      </c>
+      <c r="E38">
+        <v>4</v>
+      </c>
+      <c r="F38">
+        <v>15000</v>
+      </c>
+      <c r="G38" t="s">
+        <v>25</v>
+      </c>
+      <c r="H38" s="1">
+        <v>60000</v>
+      </c>
+      <c r="I38" s="3">
+        <v>0.12</v>
+      </c>
+      <c r="J38" s="1">
+        <f t="shared" si="1"/>
+        <v>7200</v>
+      </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="H39" s="1"/>
-      <c r="J39" s="1"/>
+      <c r="A39">
+        <v>306</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>12</v>
+      </c>
+      <c r="E39">
+        <v>2</v>
+      </c>
+      <c r="F39">
+        <v>45000</v>
+      </c>
+      <c r="G39" t="s">
+        <v>26</v>
+      </c>
+      <c r="H39" s="1">
+        <v>90000</v>
+      </c>
+      <c r="I39" s="3">
+        <v>0.18</v>
+      </c>
+      <c r="J39" s="1">
+        <f t="shared" si="1"/>
+        <v>16200</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J40" s="1">
+        <f>SUM(J34:J39)</f>
+        <v>63180</v>
+      </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
@@ -1821,6 +2064,419 @@
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44" t="s">
+        <v>7</v>
+      </c>
+      <c r="E44" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" t="s">
+        <v>73</v>
+      </c>
+      <c r="G44" t="s">
+        <v>9</v>
+      </c>
+      <c r="H44" t="e" cm="1">
+        <f t="array" ref="H44:H50">E44:E50*F44:F50</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>301</v>
+      </c>
+      <c r="B45" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" t="s">
+        <v>12</v>
+      </c>
+      <c r="E45">
+        <v>2</v>
+      </c>
+      <c r="F45">
+        <v>45000</v>
+      </c>
+      <c r="G45" t="s">
+        <v>13</v>
+      </c>
+      <c r="H45" s="1">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>302</v>
+      </c>
+      <c r="B46" t="s">
+        <v>14</v>
+      </c>
+      <c r="C46" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46">
+        <v>5</v>
+      </c>
+      <c r="F46">
+        <v>15000</v>
+      </c>
+      <c r="G46" t="s">
+        <v>17</v>
+      </c>
+      <c r="H46" s="1">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>303</v>
+      </c>
+      <c r="B47" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47" t="s">
+        <v>20</v>
+      </c>
+      <c r="E47">
+        <v>3</v>
+      </c>
+      <c r="F47">
+        <v>18000</v>
+      </c>
+      <c r="G47" t="s">
+        <v>21</v>
+      </c>
+      <c r="H47" s="1">
+        <v>54000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>304</v>
+      </c>
+      <c r="B48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C48" t="s">
+        <v>23</v>
+      </c>
+      <c r="D48" t="s">
+        <v>12</v>
+      </c>
+      <c r="E48">
+        <v>1</v>
+      </c>
+      <c r="F48">
+        <v>45000</v>
+      </c>
+      <c r="G48" t="s">
+        <v>24</v>
+      </c>
+      <c r="H48" s="1">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>305</v>
+      </c>
+      <c r="B49" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" t="s">
+        <v>11</v>
+      </c>
+      <c r="D49" t="s">
+        <v>16</v>
+      </c>
+      <c r="E49">
+        <v>4</v>
+      </c>
+      <c r="F49">
+        <v>15000</v>
+      </c>
+      <c r="G49" t="s">
+        <v>25</v>
+      </c>
+      <c r="H49" s="1">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>306</v>
+      </c>
+      <c r="B50" t="s">
+        <v>14</v>
+      </c>
+      <c r="C50" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" t="s">
+        <v>12</v>
+      </c>
+      <c r="E50">
+        <v>2</v>
+      </c>
+      <c r="F50">
+        <v>45000</v>
+      </c>
+      <c r="G50" t="s">
+        <v>26</v>
+      </c>
+      <c r="H50" s="1">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="E52">
+        <f>COUNTA(E45:E50)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A56" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>4</v>
+      </c>
+      <c r="B58" t="s">
+        <v>5</v>
+      </c>
+      <c r="C58" t="s">
+        <v>6</v>
+      </c>
+      <c r="D58" t="s">
+        <v>7</v>
+      </c>
+      <c r="E58" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" t="s">
+        <v>73</v>
+      </c>
+      <c r="G58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H58" t="e" cm="1">
+        <f t="array" ref="H58:H64">E58:E64*F58:F64</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>301</v>
+      </c>
+      <c r="B59" t="s">
+        <v>10</v>
+      </c>
+      <c r="C59" t="s">
+        <v>11</v>
+      </c>
+      <c r="D59" t="s">
+        <v>12</v>
+      </c>
+      <c r="E59">
+        <v>2</v>
+      </c>
+      <c r="F59">
+        <v>45000</v>
+      </c>
+      <c r="G59" t="s">
+        <v>13</v>
+      </c>
+      <c r="H59" s="1">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>302</v>
+      </c>
+      <c r="B60" t="s">
+        <v>14</v>
+      </c>
+      <c r="C60" t="s">
+        <v>15</v>
+      </c>
+      <c r="D60" t="s">
+        <v>16</v>
+      </c>
+      <c r="E60">
+        <v>5</v>
+      </c>
+      <c r="F60">
+        <v>15000</v>
+      </c>
+      <c r="G60" t="s">
+        <v>17</v>
+      </c>
+      <c r="H60" s="1">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>303</v>
+      </c>
+      <c r="B61" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" t="s">
+        <v>19</v>
+      </c>
+      <c r="D61" t="s">
+        <v>20</v>
+      </c>
+      <c r="E61">
+        <v>3</v>
+      </c>
+      <c r="F61">
+        <v>18000</v>
+      </c>
+      <c r="G61" t="s">
+        <v>21</v>
+      </c>
+      <c r="H61" s="1">
+        <v>54000</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>304</v>
+      </c>
+      <c r="B62" t="s">
+        <v>22</v>
+      </c>
+      <c r="C62" t="s">
+        <v>23</v>
+      </c>
+      <c r="D62" t="s">
+        <v>12</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+      <c r="F62">
+        <v>45000</v>
+      </c>
+      <c r="G62" t="s">
+        <v>24</v>
+      </c>
+      <c r="H62" s="1">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>305</v>
+      </c>
+      <c r="B63" t="s">
+        <v>10</v>
+      </c>
+      <c r="C63" t="s">
+        <v>11</v>
+      </c>
+      <c r="D63" t="s">
+        <v>16</v>
+      </c>
+      <c r="E63">
+        <v>4</v>
+      </c>
+      <c r="F63">
+        <v>15000</v>
+      </c>
+      <c r="G63" t="s">
+        <v>25</v>
+      </c>
+      <c r="H63" s="1">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>306</v>
+      </c>
+      <c r="B64" t="s">
+        <v>14</v>
+      </c>
+      <c r="C64" t="s">
+        <v>15</v>
+      </c>
+      <c r="D64" t="s">
+        <v>12</v>
+      </c>
+      <c r="E64">
+        <v>2</v>
+      </c>
+      <c r="F64">
+        <v>45000</v>
+      </c>
+      <c r="G64" t="s">
+        <v>26</v>
+      </c>
+      <c r="H64" s="1">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="66" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C66" t="s">
+        <v>76</v>
+      </c>
+      <c r="D66">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C67" t="s">
+        <v>77</v>
+      </c>
+      <c r="D67">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C68" t="s">
+        <v>78</v>
+      </c>
+      <c r="D68">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C69" t="s">
+        <v>79</v>
+      </c>
+      <c r="D69">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
